--- a/experiment/Omni+CNN_2CH_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/Omni+CNN_2CH_bestx4/Test/results-Set5/Set5.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.78</v>
+        <v>33.74</v>
       </c>
       <c r="C2" t="n">
         <v>0.8946</v>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.93</v>
+        <v>34.96</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9433</v>
+        <v>0.9434</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.46</v>
+        <v>28.69</v>
       </c>
       <c r="C4" t="n">
-        <v>0.917</v>
+        <v>0.9196</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.93</v>
+        <v>32.95</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.51</v>
+        <v>30.55</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9129</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.12</v>
+        <v>32.18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8927</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
   </sheetData>
